--- a/config/xlsx/meridians.xlsx
+++ b/config/xlsx/meridians.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>1001;3001;2001;4001;5001;6001;7001;8001;9001;10001;13101;14101;27001;27002;27003;27051;27052;27053;27101;27102;27103;27104;27105;27106;27107;27108;27109;27110;27111;27112;27113;27114;27115;27116;27117;27118;27119;27120;27121;27122;27123;27124;27125;27126;27127;27128;27129;27130;27131;27132;27133;27134;27135;27136;27137;27138;27139;27140;27141;27142;27143;27144;27145;27146;27147;27148;27149;27150;28001;28002;28017;28018;28033;28034;28049</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
@@ -498,10 +498,10 @@
         <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>101;103</t>
+          <t>1001;3001;2001;4001;5001;6001;7001;8001;9001;10001;13101;14101;27001;27002;27003;27051;27052;27053;27101;27102;27103;27104;27105;27106;27107;27108;27109;27110;27111;27112;27113;27114;27115;27116;27117;27118;27119;27120;27121;27122;27123;27124;27125;27126;27127;27128;27129;27130;27131;27132;27133;27134;27135;27136;27137;27138;27139;27140;27141;27142;27143;27144;27145;27146;27147;27148;27149;27150;28001;28002;28017;28018;28033;28034;28049;1002;3002;2002;4002;5002;6002;7002;8002;9002;10002;13102;14102;27004;27005;27006;27032;27054;27055;27056;27081;28050</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -520,7 +520,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>3</v>
@@ -532,7 +532,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>101;103</t>
+          <t>1002;3002;2002;4002;5002;6002;7002;8002;9002;10002;13102;14102;27004;27005;27006;27032;27054;27055;27056;27081;28050;1003;3003;2003;4003;5003;6003;7003;8003;9003;10003;13103;14103;27007;27008;27009;27033;27057;27058;27082;28003;28019;28035;28051</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -545,7 +545,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -554,7 +554,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>101;103</t>
+          <t>1002;3002;2002;4002;5002;6002;7002;8002;9002;10002;13102;14102;27004;27005;27006;27032;27054;27055;27056;27081;28050;1003;3003;2003;4003;5003;6003;7003;8003;9003;10003;13103;14103;27007;27008;27009;27033;27057;27058;27082;28003;28019;28035;28051</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -564,7 +564,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>4</v>
@@ -576,20 +576,20 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>101;103</t>
+          <t>1003;3003;2003;4003;5003;6003;7003;8003;9003;10003;13103;14103;27007;27008;27009;27033;27057;27058;27082;28003;28019;28035;28051;1004;3004;2004;4004;5004;6004;7004;8004;9004;10004;13104;14104;27010;27031;27059;27060;28004;28020;28036;28052</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -598,7 +598,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>101;103;61</t>
+          <t>1003;3003;2003;4003;5003;6003;7003;8003;9003;10003;13103;14103;27007;27008;27009;27033;27057;27058;27082;28003;28019;28035;28051;1004;3004;2004;4004;5004;6004;7004;8004;9004;10004;13104;14104;27010;27031;27059;27060;28004;28020;28036;28052</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -608,7 +608,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>5</v>
@@ -620,7 +620,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>101;103;61</t>
+          <t>1004;3004;2004;4004;5004;6004;7004;8004;9004;10004;13104;14104;27010;27031;27059;27060;28004;28020;28036;28052;1005;3005;2005;4005;5005;6005;7005;8005;9005;10005;13105;14105;27011;27012;27034;27061;27062;27083;28005;28021;28037;28053</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -630,10 +630,10 @@
         <v>4</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -642,17 +642,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>101;103;61</t>
+          <t>1004;3004;2004;4004;5004;6004;7004;8004;9004;10004;13104;14104;27010;27031;27059;27060;28004;28020;28036;28052;1005;3005;2005;4005;5005;6005;7005;8005;9005;10005;13105;14105;27011;27012;27034;27061;27062;27083;28005;28021;28037;28053</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>6</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>101;103;61</t>
+          <t>1005;3005;2005;4005;5005;6005;7005;8005;9005;10005;13105;14105;27011;27012;27034;27061;27062;27083;28005;28021;28037;28053;1006;3006;2006;4006;5006;6006;7006;8006;9006;10006;13106;14106;27013;27014;27035;27063;27064;27084;28006;28022;28038;28054</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -674,10 +674,10 @@
         <v>5</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -686,7 +686,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>101;103;61;62</t>
+          <t>1005;3005;2005;4005;5005;6005;7005;8005;9005;10005;13105;14105;27011;27012;27034;27061;27062;27083;28005;28021;28037;28053;1006;3006;2006;4006;5006;6006;7006;8006;9006;10006;13106;14106;27013;27014;27035;27063;27064;27084;28006;28022;28038;28054</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -696,7 +696,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>7</v>
@@ -708,20 +708,20 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>103;105;61</t>
+          <t>1006;3006;2006;4006;5006;6006;7006;8006;9006;10006;13106;14106;27013;27014;27035;27063;27064;27084;28006;28022;28038;28054;1007;3007;2007;4007;5007;6007;7007;8007;9007;10007;13107;14107;27015;27016;27017;27036;27065;27066;27067;27085;28007;28023;28039;28055</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -730,20 +730,20 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>103;105;62;63</t>
+          <t>1007;3007;2007;4007;5007;6007;7007;8007;9007;10007;13107;14107;27015;27016;27017;27036;27065;27066;27067;27085;28007;28023;28039;28055;1008;3008;2008;4008;5008;6008;7008;8008;9008;10008;13108;14108;27018;27037;27068;27086;28008;28024;28040;28056</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -752,17 +752,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>105;107;63;64</t>
+          <t>1008;3008;2008;4008;5008;6008;7008;8008;9008;10008;13108;14108;27018;27037;27068;27086;28008;28024;28040;28056;1009;3009;2009;4009;5009;6009;7009;8009;9009;10009;13109;14109;27019;27020;27038;27069;27070;27087;28009;28025;28041;28057</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>8</v>
@@ -774,20 +774,20 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>105;107;62</t>
+          <t>1009;3009;2009;4009;5009;6009;7009;8009;9009;10009;13109;14109;27019;27020;27038;27069;27070;27087;28009;28025;28041;28057;1010;3010;2010;4010;5010;6010;7010;8010;9010;10010;13110;14110;27021;27022;27039;27071;27072;27088;28010;28026;28042;28058</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -796,20 +796,20 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>105;107;63;64;65</t>
+          <t>1010;3010;2010;4010;5010;6010;7010;8010;9010;10010;13110;14110;27021;27022;27039;27071;27072;27088;28010;28026;28042;28058;1011;3011;2011;4011;5011;6011;7011;8011;9011;10011;13111;14111;27023;27024;27025;27040;27073;27074;27075;27089;27097;28011;28027;28043;28059</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -818,20 +818,20 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>107;41;65;66;67</t>
+          <t>1011;3011;2011;4011;5011;6011;7011;8011;9011;10011;13111;14111;27023;27024;27025;27040;27073;27074;27075;27089;27097;28011;28027;28043;28059;1012;3012;2012;4012;5012;6012;7012;8012;9012;10012;13112;14112;27026;27041;27049;27076;27090;27095;28012;28028;28044;28060</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -840,20 +840,20 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>107;41;66</t>
+          <t>1012;3012;2012;4012;5012;6012;7012;8012;9012;10012;13112;14112;27026;27041;27049;27076;27090;27095;28012;28028;28044;28060;1013;3013;2013;4013;5013;6013;7013;8013;9013;10013;13113;14113;27027;27028;27042;27077;27078;27091;28013;28029;28045</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -862,20 +862,20 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>107;41;42;67;68</t>
+          <t>1013;3013;2013;4013;5013;6013;7013;8013;9013;10013;13113;14113;27027;27028;27042;27077;27078;27091;28013;28029;28045;1014;3014;2014;4014;5014;6014;7014;8014;9014;10014;13114;14114;27029;27030;27043;27046;27079;27080;27092;27098;28014;28030;28046</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -884,20 +884,20 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>107;42;43;68</t>
+          <t>1014;3014;2014;4014;5014;6014;7014;8014;9014;10014;13114;14114;27029;27030;27043;27046;27079;27080;27092;27098;28014;28030;28046;1015;3015;2015;4015;5015;6015;7015;8015;9015;10015;13115;14115;27044;27048;27093;27099;28015;28031;28047</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -906,262 +906,20 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>107;43;66</t>
+          <t>1015;3015;2015;4015;5015;6015;7015;8015;9015;10015;13115;14115;27044;27048;27093;27099;28015;28031;28047;1016;3016;2016;4016;5016;6016;7016;8016;9016;10016;13116;14116;27045;27047;27050;27094;27096;27100;28016;28032;28048</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>107;43;44;67;68</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>107;44;45;68</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>107;44;66</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>107;45;67;68</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>107;45;68</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>107;45;66</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>107;45;67;68</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>107;45;68</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>107;45;66</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>107;45;67;68</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>107;45;68</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/config/xlsx/meridians.xlsx
+++ b/config/xlsx/meridians.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="meridians" sheetId="1" r:id="R9ac98fd772e3476d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="meridians" sheetId="1" r:id="R7217342320b5460a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -391,9 +391,6 @@
           <x:t xml:space="preserve">order_count</x:t>
         </x:is>
       </x:c>
-      <x:c r="G1" t="str">
-        <x:v>qi_per_value</x:v>
-      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="n">
@@ -401,7 +398,7 @@
       </x:c>
       <x:c r="B2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1001;3001;2001;4001;5001;6001;7001;8001;9001;10001;13101;14101;27001;27002;27003;27051;27052;27053;27101;27102;27103;27104;27105;27106;27107;27108;27109;27110;27111;27112;27113;27114;27115;27116;27117;27118;27119;27120;27121;27122;27123;27124;27125;27126;27127;27128;27129;27130;27131;27132;27133;27134;27135;27136;27137;27138;27139;27140;27141;27142;27143;27144;27145;27146;27147;27148;27149;27150;28001;28002;28017;28018;28033;28034;28049</x:t>
+          <x:t xml:space="preserve">1001;2001;3001;4001;5001;6001;7001;8001;9001;10001;27001;27051;27101</x:t>
         </x:is>
       </x:c>
       <x:c r="C2" s="3" t="n">
@@ -411,13 +408,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E2" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G2" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -426,7 +420,7 @@
       </x:c>
       <x:c r="B3" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1001;3001;2001;4001;5001;6001;7001;8001;9001;10001;13101;14101;27001;27002;27003;27051;27052;27053;27101;27102;27103;27104;27105;27106;27107;27108;27109;27110;27111;27112;27113;27114;27115;27116;27117;27118;27119;27120;27121;27122;27123;27124;27125;27126;27127;27128;27129;27130;27131;27132;27133;27134;27135;27136;27137;27138;27139;27140;27141;27142;27143;27144;27145;27146;27147;27148;27149;27150;28001;28002;28017;28018;28033;28034;28049;1002;3002;2002;4002;5002;6002;7002;8002;9002;10002;13102;14102;27004;27005;27006;27032;27054;27055;27056;27081;28050</x:t>
+          <x:t xml:space="preserve">1001;2001;3001;4001;5001;6001;7001;8001;9001;10001;27001;27051;27101</x:t>
         </x:is>
       </x:c>
       <x:c r="C3" s="3" t="n">
@@ -436,13 +430,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E3" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F3" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G3" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -451,7 +442,7 @@
       </x:c>
       <x:c r="B4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1002;3002;2002;4002;5002;6002;7002;8002;9002;10002;13102;14102;27004;27005;27006;27032;27054;27055;27056;27081;28050;1003;3003;2003;4003;5003;6003;7003;8003;9003;10003;13103;14103;27007;27008;27009;27033;27057;27058;27082;28003;28019;28035;28051</x:t>
+          <x:t xml:space="preserve">1002;2002;3002;4002;5002;6002;7002;8002;9002;10002;27002;27052;27102</x:t>
         </x:is>
       </x:c>
       <x:c r="C4" s="3" t="n">
@@ -461,13 +452,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E4" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F4" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G4" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -476,7 +464,7 @@
       </x:c>
       <x:c r="B5" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1002;3002;2002;4002;5002;6002;7002;8002;9002;10002;13102;14102;27004;27005;27006;27032;27054;27055;27056;27081;28050;1003;3003;2003;4003;5003;6003;7003;8003;9003;10003;13103;14103;27007;27008;27009;27033;27057;27058;27082;28003;28019;28035;28051</x:t>
+          <x:t xml:space="preserve">1002;2002;3002;4002;5002;6002;7002;8002;9002;10002;27002;27052;27102</x:t>
         </x:is>
       </x:c>
       <x:c r="C5" s="3" t="n">
@@ -486,13 +474,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E5" s="3" t="n">
-        <x:v>4</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F5" s="3" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G5" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -501,7 +486,7 @@
       </x:c>
       <x:c r="B6" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1003;3003;2003;4003;5003;6003;7003;8003;9003;10003;13103;14103;27007;27008;27009;27033;27057;27058;27082;28003;28019;28035;28051;1004;3004;2004;4004;5004;6004;7004;8004;9004;10004;13104;14104;27010;27031;27059;27060;28004;28020;28036;28052</x:t>
+          <x:t xml:space="preserve">1003;2003;3003;4003;5003;6003;7003;8003;9003;10003;27003;27053;27103;27105</x:t>
         </x:is>
       </x:c>
       <x:c r="C6" s="3" t="n">
@@ -511,13 +496,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F6" s="3" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G6" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -526,7 +508,7 @@
       </x:c>
       <x:c r="B7" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1003;3003;2003;4003;5003;6003;7003;8003;9003;10003;13103;14103;27007;27008;27009;27033;27057;27058;27082;28003;28019;28035;28051;1004;3004;2004;4004;5004;6004;7004;8004;9004;10004;13104;14104;27010;27031;27059;27060;28004;28020;28036;28052</x:t>
+          <x:t xml:space="preserve">1003;2003;3003;4003;5003;6003;7003;8003;9003;10003;27003;27053;27103;27105</x:t>
         </x:is>
       </x:c>
       <x:c r="C7" s="3" t="n">
@@ -536,13 +518,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E7" s="3" t="n">
-        <x:v>6</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F7" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G7" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -551,7 +530,7 @@
       </x:c>
       <x:c r="B8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1004;3004;2004;4004;5004;6004;7004;8004;9004;10004;13104;14104;27010;27031;27059;27060;28004;28020;28036;28052;1005;3005;2005;4005;5005;6005;7005;8005;9005;10005;13105;14105;27011;27012;27034;27061;27062;27083;28005;28021;28037;28053</x:t>
+          <x:t xml:space="preserve">1004;2004;3004;4004;5004;6004;7004;8004;9004;10004;27004;27006;27054;27104;27130;27144</x:t>
         </x:is>
       </x:c>
       <x:c r="C8" s="3" t="n">
@@ -561,13 +540,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E8" s="3" t="n">
-        <x:v>7</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F8" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G8" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -576,7 +552,7 @@
       </x:c>
       <x:c r="B9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1004;3004;2004;4004;5004;6004;7004;8004;9004;10004;13104;14104;27010;27031;27059;27060;28004;28020;28036;28052;1005;3005;2005;4005;5005;6005;7005;8005;9005;10005;13105;14105;27011;27012;27034;27061;27062;27083;28005;28021;28037;28053</x:t>
+          <x:t xml:space="preserve">1004;2004;3004;4004;5004;6004;7004;8004;9004;10004;27004;27006;27054;27104;27130;27144</x:t>
         </x:is>
       </x:c>
       <x:c r="C9" s="3" t="n">
@@ -586,13 +562,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E9" s="3" t="n">
-        <x:v>8</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F9" s="3" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G9" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -601,7 +574,7 @@
       </x:c>
       <x:c r="B10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1005;3005;2005;4005;5005;6005;7005;8005;9005;10005;13105;14105;27011;27012;27034;27061;27062;27083;28005;28021;28037;28053;1006;3006;2006;4006;5006;6006;7006;8006;9006;10006;13106;14106;27013;27014;27035;27063;27064;27084;28006;28022;28038;28054</x:t>
+          <x:t xml:space="preserve">1005;2005;3005;4005;5005;6005;7005;8005;9005;10005;27005;27007;27055;27061;27106;27118;27139</x:t>
         </x:is>
       </x:c>
       <x:c r="C10" s="3" t="n">
@@ -611,13 +584,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E10" s="3" t="n">
-        <x:v>9</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F10" s="3" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G10" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -626,7 +596,7 @@
       </x:c>
       <x:c r="B11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1005;3005;2005;4005;5005;6005;7005;8005;9005;10005;13105;14105;27011;27012;27034;27061;27062;27083;28005;28021;28037;28053;1006;3006;2006;4006;5006;6006;7006;8006;9006;10006;13106;14106;27013;27014;27035;27063;27064;27084;28006;28022;28038;28054</x:t>
+          <x:t xml:space="preserve">1005;2005;3005;4005;5005;6005;7005;8005;9005;10005;27005;27007;27055;27061;27106;27118;27139</x:t>
         </x:is>
       </x:c>
       <x:c r="C11" s="3" t="n">
@@ -636,13 +606,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E11" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F11" s="3" t="n">
         <x:v>7</x:v>
-      </x:c>
-      <x:c r="G11" t="n">
-        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -651,7 +618,7 @@
       </x:c>
       <x:c r="B12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1006;3006;2006;4006;5006;6006;7006;8006;9006;10006;13106;14106;27013;27014;27035;27063;27064;27084;28006;28022;28038;28054;1007;3007;2007;4007;5007;6007;7007;8007;9007;10007;13107;14107;27015;27016;27017;27036;27065;27066;27067;27085;28007;28023;28039;28055</x:t>
+          <x:t xml:space="preserve">1006;2006;3006;4006;5006;6006;7006;8006;9006;10006;27008;27056;27062;27107;27119;27140</x:t>
         </x:is>
       </x:c>
       <x:c r="C12" s="3" t="n">
@@ -661,13 +628,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E12" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F12" s="3" t="n">
         <x:v>7</x:v>
-      </x:c>
-      <x:c r="G12" t="n">
-        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -676,7 +640,7 @@
       </x:c>
       <x:c r="B13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1007;3007;2007;4007;5007;6007;7007;8007;9007;10007;13107;14107;27015;27016;27017;27036;27065;27066;27067;27085;28007;28023;28039;28055;1008;3008;2008;4008;5008;6008;7008;8008;9008;10008;13108;14108;27018;27037;27068;27086;28008;28024;28040;28056</x:t>
+          <x:t xml:space="preserve">1007;2007;3007;4007;5007;6007;7007;8007;9007;10007;27009;27057;27063;27108;27120;27141</x:t>
         </x:is>
       </x:c>
       <x:c r="C13" s="3" t="n">
@@ -686,13 +650,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E13" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F13" s="3" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G13" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -701,7 +662,7 @@
       </x:c>
       <x:c r="B14" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1008;3008;2008;4008;5008;6008;7008;8008;9008;10008;13108;14108;27018;27037;27068;27086;28008;28024;28040;28056;1009;3009;2009;4009;5009;6009;7009;8009;9009;10009;13109;14109;27019;27020;27038;27069;27070;27087;28009;28025;28041;28057</x:t>
+          <x:t xml:space="preserve">1008;2008;3008;4008;5008;6008;7008;8008;9008;10008;27010;27058;27064;27109;27121;27142;27147</x:t>
         </x:is>
       </x:c>
       <x:c r="C14" s="3" t="n">
@@ -711,13 +672,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E14" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F14" s="3" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G14" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -726,7 +684,7 @@
       </x:c>
       <x:c r="B15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1009;3009;2009;4009;5009;6009;7009;8009;9009;10009;13109;14109;27019;27020;27038;27069;27070;27087;28009;28025;28041;28057;1010;3010;2010;4010;5010;6010;7010;8010;9010;10010;13110;14110;27021;27022;27039;27071;27072;27088;28010;28026;28042;28058</x:t>
+          <x:t xml:space="preserve">1009;2009;3009;4009;5009;6009;7009;8009;9009;10009;27011;27015;27059;27065;27069;27110;27122;27131</x:t>
         </x:is>
       </x:c>
       <x:c r="C15" s="3" t="n">
@@ -736,13 +694,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E15" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F15" s="3" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G15" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -751,7 +706,7 @@
       </x:c>
       <x:c r="B16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1010;3010;2010;4010;5010;6010;7010;8010;9010;10010;13110;14110;27021;27022;27039;27071;27072;27088;28010;28026;28042;28058;1011;3011;2011;4011;5011;6011;7011;8011;9011;10011;13111;14111;27023;27024;27025;27040;27073;27074;27075;27089;27097;28011;28027;28043;28059</x:t>
+          <x:t xml:space="preserve">1010;2010;3010;4010;5010;6010;7010;8010;9010;10010;27012;27016;27060;27066;27070;27111;27123;27132;27145</x:t>
         </x:is>
       </x:c>
       <x:c r="C16" s="3" t="n">
@@ -761,13 +716,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E16" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F16" s="3" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G16" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -776,7 +728,7 @@
       </x:c>
       <x:c r="B17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1011;3011;2011;4011;5011;6011;7011;8011;9011;10011;13111;14111;27023;27024;27025;27040;27073;27074;27075;27089;27097;28011;28027;28043;28059;1012;3012;2012;4012;5012;6012;7012;8012;9012;10012;13112;14112;27026;27041;27049;27076;27090;27095;28012;28028;28044;28060</x:t>
+          <x:t xml:space="preserve">1011;2011;3011;4011;5011;6011;7011;8011;9011;10011;27013;27017;27020;27021;27067;27071;27112;27124;27133;27146</x:t>
         </x:is>
       </x:c>
       <x:c r="C17" s="3" t="n">
@@ -786,13 +738,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E17" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F17" s="3" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G17" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -801,7 +750,7 @@
       </x:c>
       <x:c r="B18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1012;3012;2012;4012;5012;6012;7012;8012;9012;10012;13112;14112;27026;27041;27049;27076;27090;27095;28012;28028;28044;28060;1013;3013;2013;4013;5013;6013;7013;8013;9013;10013;13113;14113;27027;27028;27042;27077;27078;27091;28013;28029;28045</x:t>
+          <x:t xml:space="preserve">1012;2012;3012;4012;5012;6012;7012;8012;9012;10012;27014;27018;27019;27022;27068;27072;27113;27125;27134;27143</x:t>
         </x:is>
       </x:c>
       <x:c r="C18" s="3" t="n">
@@ -811,13 +760,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E18" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F18" s="3" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G18" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -826,7 +772,7 @@
       </x:c>
       <x:c r="B19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1013;3013;2013;4013;5013;6013;7013;8013;9013;10013;13113;14113;27027;27028;27042;27077;27078;27091;28013;28029;28045;1014;3014;2014;4014;5014;6014;7014;8014;9014;10014;13114;14114;27029;27030;27043;27046;27079;27080;27092;27098;28014;28030;28046</x:t>
+          <x:t xml:space="preserve">1013;2013;3013;4013;5013;6013;7013;8013;9013;10013;27023;27027;27073;27077;27114;27126;27135</x:t>
         </x:is>
       </x:c>
       <x:c r="C19" s="3" t="n">
@@ -836,13 +782,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E19" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F19" s="3" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G19" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -851,7 +794,7 @@
       </x:c>
       <x:c r="B20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1014;3014;2014;4014;5014;6014;7014;8014;9014;10014;13114;14114;27029;27030;27043;27046;27079;27080;27092;27098;28014;28030;28046;1015;3015;2015;4015;5015;6015;7015;8015;9015;10015;13115;14115;27044;27048;27093;27099;28015;28031;28047</x:t>
+          <x:t xml:space="preserve">1014;2014;3014;4014;5014;6014;7014;8014;9014;10014;27024;27028;27074;27078;27115;27127;27136;27148</x:t>
         </x:is>
       </x:c>
       <x:c r="C20" s="3" t="n">
@@ -861,13 +804,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E20" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F20" s="3" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G20" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -876,7 +816,7 @@
       </x:c>
       <x:c r="B21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1015;3015;2015;4015;5015;6015;7015;8015;9015;10015;13115;14115;27044;27048;27093;27099;28015;28031;28047;1016;3016;2016;4016;5016;6016;7016;8016;9016;10016;13116;14116;27045;27047;27050;27094;27096;27100;28016;28032;28048</x:t>
+          <x:t xml:space="preserve">1015;2015;3015;4015;5015;6015;7015;8015;9015;10015;27025;27029;27075;27079;27116;27128;27137;27149</x:t>
         </x:is>
       </x:c>
       <x:c r="C21" s="3" t="n">
@@ -886,13 +826,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E21" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F21" s="3" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G21" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/config/xlsx/meridians.xlsx
+++ b/config/xlsx/meridians.xlsx
@@ -2,10 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet name="meridians" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -15,12 +20,14 @@
   <fonts count="2">
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -33,12 +40,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
@@ -62,8 +76,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -178,14 +193,72 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Calibri Light"/>
-        <a:cs typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -241,7 +314,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -250,13 +323,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -290,6 +363,17 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -344,6 +428,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -353,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -395,6 +481,11 @@
           <t>order_count</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fixed_orders</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -402,20 +493,25 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1004;2004;3004;4004;5004;6004;7004;8004;9004;10004;27001;27002;27003;27004;27006;27051;27052;27053;27054;27101;27102;27103;27104;27105;27130;27144</t>
+          <t>5004;6001</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>219</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>[{"item_ids":[5004]},{"item_ids":[6001]},{"item_ids":[9004]},{"item_ids":[10001]},{"item_ids":[27001]}]</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -837,6 +933,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/config/xlsx/meridians.xlsx
+++ b/config/xlsx/meridians.xlsx
@@ -87,7 +87,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,13 +99,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -579,148 +572,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1549,7 +1542,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2">
         <v>10</v>
